--- a/data/trans_orig/IP18A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35677</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62814</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52625</t>
+          <t>52675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63788</t>
+          <t>63876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109776</t>
+          <t>108963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125119</t>
+          <t>124599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72483</t>
+          <t>71683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98112</t>
+          <t>97320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>64034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89715</t>
+          <t>89512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143510</t>
+          <t>142875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177492</t>
+          <t>178633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274214</t>
+          <t>275006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299843</t>
+          <t>300643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319596</t>
+          <t>319799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345716</t>
+          <t>345277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>604145</t>
+          <t>603004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638127</t>
+          <t>638762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34498</t>
+          <t>34585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51022</t>
+          <t>51782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>42668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>65573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90698</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103272</t>
+          <t>102512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119796</t>
+          <t>119709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97241</t>
+          <t>97253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113426</t>
+          <t>112364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203517</t>
+          <t>204260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229894</t>
+          <t>228642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123195</t>
+          <t>123311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157361</t>
+          <t>156291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110039</t>
+          <t>110606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142139</t>
+          <t>141773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244973</t>
+          <t>241272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289395</t>
+          <t>289498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>440657</t>
+          <t>441727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>474823</t>
+          <t>474707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481149</t>
+          <t>481515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513249</t>
+          <t>512682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>931911</t>
+          <t>931808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>976333</t>
+          <t>980034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27283</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>42640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72099</t>
+          <t>72160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57157</t>
+          <t>57026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68779</t>
+          <t>68225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121425</t>
+          <t>120338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138915</t>
+          <t>137414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79257</t>
+          <t>79136</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107911</t>
+          <t>107920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67898</t>
+          <t>67754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96948</t>
+          <t>96656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155928</t>
+          <t>155420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193435</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313088</t>
+          <t>313079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341742</t>
+          <t>341863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370204</t>
+          <t>370496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>399254</t>
+          <t>399398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694717</t>
+          <t>693653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732224</t>
+          <t>732732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>30296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>54956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80086</t>
+          <t>78567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120266</t>
+          <t>119611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135685</t>
+          <t>135602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116536</t>
+          <t>117283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133851</t>
+          <t>134740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241016</t>
+          <t>242535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266259</t>
+          <t>266146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121942</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157901</t>
+          <t>157209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117878</t>
+          <t>115790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152555</t>
+          <t>150430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252276</t>
+          <t>250582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301596</t>
+          <t>298674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505156</t>
+          <t>505848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>541115</t>
+          <t>540966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>556619</t>
+          <t>558744</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>591296</t>
+          <t>593384</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070635</t>
+          <t>1073557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1119955</t>
+          <t>1121649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,74%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47789</t>
+          <t>48071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44285</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54594</t>
+          <t>54734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86167</t>
+          <t>86472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99637</t>
+          <t>100003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63254</t>
+          <t>63577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89000</t>
+          <t>89416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72031</t>
+          <t>72889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98739</t>
+          <t>99272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>142483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179761</t>
+          <t>178904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344379</t>
+          <t>343963</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370125</t>
+          <t>369802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338090</t>
+          <t>337557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364798</t>
+          <t>363940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690447</t>
+          <t>691304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728551</t>
+          <t>727725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28347</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>44997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43343</t>
+          <t>43927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58469</t>
+          <t>58706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81949</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107632</t>
+          <t>108233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124883</t>
+          <t>125219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127682</t>
+          <t>127098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144505</t>
+          <t>145201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242306</t>
+          <t>241307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265786</t>
+          <t>265549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>106331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137208</t>
+          <t>139069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115814</t>
+          <t>113675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229916</t>
+          <t>231019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>277629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504061</t>
+          <t>502200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>535067</t>
+          <t>534938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522158</t>
+          <t>522788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>554105</t>
+          <t>556244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1033871</t>
+          <t>1033559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1081272</t>
+          <t>1080169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44983</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>64341</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>77903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113885</t>
+          <t>113584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131371</t>
+          <t>131048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>53502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86784</t>
+          <t>86709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98227</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113645</t>
+          <t>113120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177324</t>
+          <t>177360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196505</t>
+          <t>197811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10140</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20805</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12859</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8284</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18723</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18937</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>35999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59070</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53251</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63916</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58538</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52674</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63113</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52460</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63573</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59070</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52675</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63876</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,76%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108963</t>
+          <t>109454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124599</t>
+          <t>125008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>76299</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63311</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>89353</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>84325</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>71683</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>97320</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>72175</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>96919</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>76299</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>64034</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>89512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142875</t>
+          <t>143687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178633</t>
+          <t>178317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>333012</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>319958</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>346000</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>288001</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>275006</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>300643</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>275407</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>300151</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>333012</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>319799</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>345277</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>603004</t>
+          <t>603320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638762</t>
+          <t>637950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>561</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34555</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26748</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43972</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>42455</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34585</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51782</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34136</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51440</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34555</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27557</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>42668</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89955</t>
+          <t>89112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95949</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>113173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>75,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>111839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>102512</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>119709</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102854</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>120158</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>72,48%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105366</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>97253</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>112364</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>75,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204260</t>
+          <t>205103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228642</t>
+          <t>229216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>125839</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>109801</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>142771</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>123311</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>156291</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>122547</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>156306</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>125839</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>110606</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>141773</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241272</t>
+          <t>242263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289498</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>497449</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>480517</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>513487</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>680</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>458378</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>441727</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>474707</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>441712</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>475471</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>497449</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>481515</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>512682</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>931808</t>
+          <t>931087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>980034</t>
+          <t>979043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2012 (tasa de respuesta: 98,2%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2012 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13137</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8048</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19367</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>20047</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13832</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26764</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14432</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27103</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13137</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8761</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19960</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42640</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63849</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57619</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68938</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>65945</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59228</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72160</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>58889</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71560</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>83,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63849</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57026</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68225</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,94%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120338</t>
+          <t>120404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137414</t>
+          <t>137558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>85992</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>85992</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>85992</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81464</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68489</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>96393</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92664</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>79136</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>107920</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>78967</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>106049</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>81464</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67754</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>96656</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155420</t>
+          <t>157039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>196256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>385688</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>370759</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>398663</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>328335</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>313079</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>341863</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>314950</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>342032</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>385688</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>370496</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>399398</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>82,56%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>693653</t>
+          <t>691896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732732</t>
+          <t>731113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>467152</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>467152</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>467152</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>420999</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>420999</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>420999</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>467152</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>467152</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>467152</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38957</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30543</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48726</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27099</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20464</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36455</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19788</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35688</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>38957</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30296</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>47753</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>54835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78567</t>
+          <t>80189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126079</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>116310</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>134493</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>128967</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119611</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135602</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>120378</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>136278</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>126079</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>117283</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>134740</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242535</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266146</t>
+          <t>266267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165036</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165036</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>133559</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>117557</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>151268</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>122091</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>157209</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>123450</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>156938</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>133559</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>115790</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>150430</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>250582</t>
+          <t>249074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>298674</t>
+          <t>297172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>575615</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>557906</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>591617</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>523247</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>505848</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>540966</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>506119</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>539607</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>78,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>575615</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>558744</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>593384</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1073557</t>
+          <t>1075059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1121649</t>
+          <t>1123157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>709174</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>709174</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>709174</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>663057</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>663057</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>663057</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>709174</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>709174</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>709174</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2016 (tasa de respuesta: 98,26%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2016 (tasa de respuesta: 98,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>12013</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18060</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>10834</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6589</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16293</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15965</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12013</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7331</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17601</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50052</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44005</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54864</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43826</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38367</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48071</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>38695</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48212</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50052</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44464</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54734</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86472</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100003</t>
+          <t>100344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84875</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>73065</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>100377</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>75479</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>63577</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>89416</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>62942</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>88431</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>84875</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>72889</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>99272</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142483</t>
+          <t>144452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178904</t>
+          <t>178785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>351954</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>336452</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>363764</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>357900</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>343963</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>369802</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>344948</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>370437</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>351954</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>337557</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>363940</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691304</t>
+          <t>691423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727725</t>
+          <t>725756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>436829</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>436829</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>436829</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>433379</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>433379</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>433379</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>436829</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>436829</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>436829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34147</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27098</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43387</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28011</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44997</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27766</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45483</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34147</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25824</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>43927</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58706</t>
+          <t>58655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82948</t>
+          <t>82258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136878</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127638</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>143927</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>117415</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>108233</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>125219</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107747</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>125464</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136878</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>127098</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145201</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241307</t>
+          <t>241997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265549</t>
+          <t>265600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171025</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171025</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>153230</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>153230</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>153230</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171025</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171025</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115286</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>148676</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>106331</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>139069</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>104847</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>137562</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>113675</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>147131</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231019</t>
+          <t>231902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277629</t>
+          <t>275777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>538884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>521243</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>554633</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>519141</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>502200</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>534938</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>503707</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>536422</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>538884</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>522788</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>556244</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1033559</t>
+          <t>1035411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1080169</t>
+          <t>1079286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>967</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>641269</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>641269</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>641269</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2789</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3626</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>323</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8490</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3756</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>55,72%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5808</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9434</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18036</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12318</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25515</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15350</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10110</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21897</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26908</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34478</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65771</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>58292</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71489</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>50888</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44341</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56128</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>72121</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77903</t>
+          <t>53095</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>123009</t>
+          <t>113313</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113584</t>
+          <t>103375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131048</t>
+          <t>121595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4928</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9139</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>12681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19685</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26513</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24631</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21499</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26572</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50274</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17290</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32281</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13605</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26560</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>53446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98157</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89441</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104432</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>81085</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73754</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86709</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>80,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>106550</t>
+          <t>76012</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98745</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113120</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>187635</t>
+          <t>174169</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177360</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197811</t>
+          <t>182968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
